--- a/backend/scheduler/services/resource/data/validation/telescope_schedules.xlsx
+++ b/backend/scheduler/services/resource/data/validation/telescope_schedules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bmiller/python/scheduler/backend/scheduler/services/resource/data/validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7A96A4-7EC2-1A46-B0A3-0DEC1C93487D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6405B2E-F42D-0A42-8049-3B0F14D394AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -284,7 +284,7 @@
     <t>Queue | Visitor: `Alopeke</t>
   </si>
   <si>
-    <t>Classical: GS-2014B-C-500, GS-2014B-C-502</t>
+    <t>Classical: GS-2018B-C-500, GS-2018B-C-502</t>
   </si>
 </sst>
 </file>
